--- a/insights/20251230-20241230-insights/Comparison_Visits.xlsx
+++ b/insights/20251230-20241230-insights/Comparison_Visits.xlsx
@@ -448,7 +448,7 @@
         <v>46021</v>
       </c>
       <c r="C3" s="2">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -476,10 +476,10 @@
         <v>46021</v>
       </c>
       <c r="C5" s="2">
-        <v>603</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,10 +490,10 @@
         <v>46021</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>603</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,7 +504,7 @@
         <v>46021</v>
       </c>
       <c r="C7" s="2">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -532,10 +532,10 @@
         <v>46021</v>
       </c>
       <c r="C9" s="2">
-        <v>3</v>
+        <v>1715</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,10 +546,10 @@
         <v>46021</v>
       </c>
       <c r="C10" s="2">
-        <v>1717</v>
+        <v>451</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +560,10 @@
         <v>46021</v>
       </c>
       <c r="C11" s="2">
-        <v>451</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
